--- a/Книга1 обновленный.xlsx
+++ b/Книга1 обновленный.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CFBEBC-D7DC-4FED-B5C7-AE3A89D56D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0340F7D-7975-44E7-BA1A-74833929EB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0B8518B6-2F67-4CC3-9270-DDD2C69E897A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="1201">
   <si>
     <t>DaData</t>
   </si>
@@ -3809,12 +3809,24 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -3844,7 +3856,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3872,6 +3884,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4250,7 +4271,7 @@
       <c r="B3" s="9" t="s">
         <v>512</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="13" t="s">
         <v>607</v>
       </c>
       <c r="D3" s="10" t="s">
@@ -4271,7 +4292,7 @@
       <c r="B4" s="9" t="s">
         <v>359</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="13" t="s">
         <v>608</v>
       </c>
       <c r="D4" s="10" t="s">
@@ -4292,7 +4313,7 @@
       <c r="B5" s="9" t="s">
         <v>360</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="13" t="s">
         <v>609</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -4313,7 +4334,7 @@
       <c r="B6" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="13" t="s">
         <v>610</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -4334,7 +4355,7 @@
       <c r="B7" s="9" t="s">
         <v>362</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="13" t="s">
         <v>611</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -4499,7 +4520,7 @@
       <c r="A15" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="11" t="s">
         <v>370</v>
       </c>
       <c r="C15" s="10" t="s">
@@ -4541,7 +4562,7 @@
       <c r="A17" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="11" t="s">
         <v>372</v>
       </c>
       <c r="C17" s="10" t="s">
@@ -4604,7 +4625,7 @@
       <c r="A20" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="11" t="s">
         <v>375</v>
       </c>
       <c r="C20" s="10" t="s">
@@ -4877,7 +4898,7 @@
       <c r="A33" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="11" t="s">
         <v>388</v>
       </c>
       <c r="C33" s="10" t="s">
@@ -5675,7 +5696,7 @@
       <c r="A71" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="11" t="s">
         <v>523</v>
       </c>
       <c r="C71" s="10" t="s">
@@ -5738,7 +5759,7 @@
       <c r="A74" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="11" t="s">
         <v>526</v>
       </c>
       <c r="C74" s="10" t="s">
@@ -6350,7 +6371,7 @@
       <c r="C104" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="D104" s="12" t="s">
         <v>335</v>
       </c>
       <c r="E104" s="10"/>
@@ -6365,13 +6386,13 @@
       <c r="A105" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="11" t="s">
         <v>225</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" s="12" t="s">
         <v>336</v>
       </c>
       <c r="E105" s="10"/>
@@ -6434,7 +6455,7 @@
       <c r="C108" s="10" t="s">
         <v>713</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" s="12" t="s">
         <v>339</v>
       </c>
       <c r="E108" s="10"/>
@@ -6512,7 +6533,7 @@
       <c r="A112" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" s="11" t="s">
         <v>218</v>
       </c>
       <c r="C112" s="10" t="s">
@@ -6701,7 +6722,7 @@
       <c r="A121" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B121" s="9" t="s">
+      <c r="B121" s="11" t="s">
         <v>210</v>
       </c>
       <c r="C121" s="10" t="s">
@@ -7197,7 +7218,7 @@
       <c r="A143" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="11" t="s">
         <v>234</v>
       </c>
       <c r="C143" s="10" t="s">
@@ -7565,7 +7586,7 @@
       <c r="A159" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B159" s="9" t="s">
+      <c r="B159" s="11" t="s">
         <v>234</v>
       </c>
       <c r="C159" s="10" t="s">
@@ -7634,7 +7655,7 @@
       <c r="A162" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="B162" s="9" t="s">
+      <c r="B162" s="11" t="s">
         <v>568</v>
       </c>
       <c r="C162" s="10" t="s">
@@ -7680,7 +7701,7 @@
       <c r="A164" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B164" s="11" t="s">
         <v>570</v>
       </c>
       <c r="C164" s="10" t="s">
@@ -7864,7 +7885,7 @@
       <c r="A172" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B172" s="9" t="s">
+      <c r="B172" s="11" t="s">
         <v>577</v>
       </c>
       <c r="C172" s="10" t="s">
@@ -8163,7 +8184,7 @@
       <c r="A185" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="B185" s="9" t="s">
+      <c r="B185" s="11" t="s">
         <v>588</v>
       </c>
       <c r="C185" s="10" t="s">
@@ -8186,7 +8207,7 @@
       <c r="A186" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B186" s="9" t="s">
+      <c r="B186" s="11" t="s">
         <v>589</v>
       </c>
       <c r="C186" s="10" t="s">
@@ -8370,7 +8391,7 @@
       <c r="A194" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B194" s="9" t="s">
+      <c r="B194" s="11" t="s">
         <v>597</v>
       </c>
       <c r="C194" s="10" t="s">
